--- a/vocoder-pico-hardware_BOM.xlsx
+++ b/vocoder-pico-hardware_BOM.xlsx
@@ -342,7 +342,7 @@
     <t xml:space="preserve">Omron</t>
   </si>
   <si>
-    <t xml:space="preserve">B3F-1000</t>
+    <t xml:space="preserve">B3F-1060</t>
   </si>
   <si>
     <t xml:space="preserve">SWITCH TACTILE SPST-NO 6X6MM</t>
@@ -465,58 +465,58 @@
     <t xml:space="preserve">PJ398SM vertical</t>
   </si>
   <si>
+    <t xml:space="preserve">Align with front panel before soldering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RV1,RV2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RD901F-40 B10K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POT 9MM VERTICAL 10K LINEAR, M7 BUSHING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha RD901F-40-00D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaft type to match knobs; align with front panel before soldering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INMP441 breakout module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2S MEMS MICROPHONE MODULE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INMP441 module 2x3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sound port side facing front panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raspberry Pi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raspberry Pi Pico H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICROCONTROLLER MODULE RP2040 WITH HEADERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pico module</t>
+  </si>
+  <si>
     <t xml:space="preserve">DNS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align with front panel before soldering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RV1,RV2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RD901F-40 B10K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POT 9MM VERTICAL 10K LINEAR, M7 BUSHING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha RD901F-40-00D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaft type to match knobs; align with front panel before soldering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INMP441 breakout module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2S MEMS MICROPHONE MODULE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INMP441 module 2x3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sound port side facing front panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raspberry Pi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raspberry Pi Pico H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICROCONTROLLER MODULE RP2040 WITH HEADERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pico module</t>
   </si>
   <si>
     <t xml:space="preserve">Do not stuff – plugged into female headers by customer</t>
@@ -1936,10 +1936,10 @@
         <v>146</v>
       </c>
       <c r="H36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I36" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1947,28 +1947,28 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="H37" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1976,7 +1976,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>1</v>
@@ -1985,19 +1985,19 @@
         <v>137</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="G38" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="H38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,25 +2005,25 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="F39" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="G39" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>165</v>
